--- a/www/flightdata/xlsx/eoss-333.xlsx
+++ b/www/flightdata/xlsx/eoss-333.xlsx
@@ -3021,7 +3021,7 @@
         <v>28106.52</v>
       </c>
       <c r="I2">
-        <v>512</v>
+        <v>367</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
